--- a/artfynd/A 29052-2026 artfynd.xlsx
+++ b/artfynd/A 29052-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136349077</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136349078</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136349080</v>
       </c>
       <c r="B5" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29052-2026 artfynd.xlsx
+++ b/artfynd/A 29052-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136349077</v>
       </c>
       <c r="B3" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136349078</v>
       </c>
       <c r="B4" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136349080</v>
       </c>
       <c r="B5" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29052-2026 artfynd.xlsx
+++ b/artfynd/A 29052-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136349077</v>
       </c>
       <c r="B3" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136349078</v>
       </c>
       <c r="B4" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136349080</v>
       </c>
       <c r="B5" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
